--- a/ArchivosExcel/DireccionesRevisadas.xlsx
+++ b/ArchivosExcel/DireccionesRevisadas.xlsx
@@ -425,46 +425,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>País LATAM</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Ciudad</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Estado / Provincia / Departamento</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Google_Name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Google_Address</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Postal_Code</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Search_Query</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Search_Status</t>
         </is>
@@ -473,32 +478,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>IMSS Hospital Centro Medico Siglo XXI</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
         <is>
           <t>Centro Médico Nacional Siglo XXI</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Av. Cuauhtémoc 330, Doctores, Cuauhtémoc, 06720 Ciudad de México, CDMX, México</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>06720</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>IMSS Hospital Centro Medico Siglo XXI</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
+        <is>
+          <t>MX IMSS Hospital Centro Medico Siglo XXI</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -507,36 +517,41 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Ángeles Metropolitano</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Ciudad de México</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
         <is>
           <t>Hospital Angeles Metropolitano</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Tlacotalpan 59, Centro Urbano Pdte. Juárez, Roma Sur, Cuauhtémoc, 06760 Cuauhtémoc, CDMX, México</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>Tlacotalpan 59, Centro Urbano Pdte. Juárez, Roma Sur, Cuauhtémoc, 06760 Cuauhtémoc, CDMX</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>06760</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Ángeles Metropolitano Ciudad de México</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
+        <is>
+          <t>MX Ángeles Metropolitano Ciudad de México</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -545,38 +560,129 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Hospital de alta especialidad del Bajío</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
         <is>
           <t>Guanajuato</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Hospital Regional de Alta Especialidad del Bajío</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Blvd. Milenio 130, San Carlos la Roncha, 37544 León de los Aldama, Gto.</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>37544</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Hospital de alta especialidad del Bajío Guanajuato</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>MX Hospital de alta especialidad del Bajío Guanajuato</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Hospital General de Agudos José María Ramos Mejía</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Hospital General de Agudos José María Ramos Mejía</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gral. Urquiza 609, C1221ADC Cdad. Autónoma de Buenos Aires, Argentina</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Postal code not found</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>AR Hospital General de Agudos José María Ramos Mejía Buenos Aires</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ADDRESS FOUND - CP REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Hosítal Universitario San Antonio</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Hospital Universitario Nacional de Colombia</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Única sede, Cl. 44 #59 -75, Teusaquillo, Bogotá, Cundinamarca, Colombia</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Postal code not found</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>CO Hosítal Universitario San Antonio Bogotá</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ADDRESS FOUND - CP REVIEW</t>
         </is>
       </c>
     </row>

--- a/ArchivosExcel/DireccionesRevisadas.xlsx
+++ b/ArchivosExcel/DireccionesRevisadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,10 +466,20 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Latitude</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Search_Query</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Search_Status</t>
         </is>
@@ -495,7 +505,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Av. Cuauhtémoc 330, Doctores, Cuauhtémoc, 06720 Ciudad de México, CDMX, México</t>
+          <t>Av. Cuauhtémoc 330, Doctores, Cuauhtémoc, 06720 Ciudad de México, CDMX</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -503,12 +513,18 @@
           <t>06720</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>MX IMSS Hospital Centro Medico Siglo XXI</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H2" t="n">
+        <v>19.4083431</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-99.1539944</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>IMSS Hospital Centro Medico Siglo XXI</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -546,14 +562,16 @@
           <t>06760</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>MX Ángeles Metropolitano Ciudad de México</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Ángeles Metropolitano Ciudad de México</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ADDRESS FOUND - COORDINATES REVIEW</t>
         </is>
       </c>
     </row>
@@ -589,100 +607,16 @@
           <t>37544</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>MX Hospital de alta especialidad del Bajío Guanajuato</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Hospital General de Agudos José María Ramos Mejía</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Buenos Aires</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Hospital General de Agudos José María Ramos Mejía</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Gral. Urquiza 609, C1221ADC Cdad. Autónoma de Buenos Aires, Argentina</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Postal code not found</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>AR Hospital General de Agudos José María Ramos Mejía Buenos Aires</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>ADDRESS FOUND - CP REVIEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Hosítal Universitario San Antonio</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bogotá</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Hospital Universitario Nacional de Colombia</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Única sede, Cl. 44 #59 -75, Teusaquillo, Bogotá, Cundinamarca, Colombia</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Postal code not found</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>CO Hosítal Universitario San Antonio Bogotá</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>ADDRESS FOUND - CP REVIEW</t>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Hospital de alta especialidad del Bajío</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ADDRESS FOUND - COORDINATES REVIEW</t>
         </is>
       </c>
     </row>

--- a/ArchivosExcel/DireccionesRevisadas.xlsx
+++ b/ArchivosExcel/DireccionesRevisadas.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,61 +413,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>País LATAM</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Ciudad</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Estado / Provincia / Departamento</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Google_Name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Google_Address</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Postal_Code</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Longitude</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Coordinate_Source</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>Search_Query</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Search_Status</t>
         </is>
@@ -521,10 +514,15 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>IMSS Hospital Centro Medico Siglo XXI</t>
+          <t>RESULT_LINK_EXACT</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
+        <is>
+          <t>IMSS Hospital Centro Medico Siglo XXI MX</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -562,16 +560,25 @@
           <t>06760</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>19.4067971</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-99.16687090000001</v>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Ángeles Metropolitano Ciudad de México</t>
+          <t>CURRENT_URL_EXACT</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>ADDRESS FOUND - COORDINATES REVIEW</t>
+          <t>Ángeles Metropolitano Ciudad de México MX</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -607,16 +614,25 @@
           <t>37544</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>21.0613592</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-101.5766002</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Hospital de alta especialidad del Bajío</t>
+          <t>CURRENT_URL_EXACT</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>ADDRESS FOUND - COORDINATES REVIEW</t>
+          <t>Hospital de alta especialidad del Bajío Guanajuato MX</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>

--- a/ArchivosExcel/DireccionesRevisadas.xlsx
+++ b/ArchivosExcel/DireccionesRevisadas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,6 +474,11 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>Country_Normalized</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>Search_Status</t>
         </is>
       </c>
@@ -481,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -519,10 +524,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>IMSS Hospital Centro Medico Siglo XXI MX</t>
+          <t>IMSS Hospital Centro Medico Siglo XXI Mexico</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
+        <is>
+          <t>mexico</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -531,7 +541,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -573,10 +583,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Ángeles Metropolitano Ciudad de México MX</t>
+          <t>Ángeles Metropolitano Ciudad de México Mexico</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
+        <is>
+          <t>mexico</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -585,7 +600,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,10 +642,255 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Hospital de alta especialidad del Bajío Guanajuato MX</t>
+          <t>Hospital de alta especialidad del Bajío Guanajuato Mexico</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
+        <is>
+          <t>mexico</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Hospital Italiano de Buenos Aires</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Ciudad Autónoma de Buenos Aires</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Hospital Italiano de Buenos Aires</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tte. Gral. Juan Domingo Perón 4190, C1199 Cdad. Autónoma de Buenos Aires, Argentina</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Postal code not found</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>-34.6062243</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-58.4256399</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>RESULT_LINK_EXACT</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Hospital Italiano de Buenos Aires Buenos Aires Ciudad Autónoma de Buenos Aires Argentina</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>argentina</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>ADDRESS FOUND - CP REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Fundación Santa Fe de Bogotá</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Fundación Santa Fe de Bogotá</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>110111, Bogotá, Colombia</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>110111</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>4.6956426</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-74.033027</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>RESULT_LINK_EXACT</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Fundación Santa Fe de Bogotá Bogotá Colombia</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>colombia</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Edgardo Rebagliati Martins National Hospital</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Hospital Edgardo Rebagliati Martins</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Av. Edgardo Rebagliati 490, Peru 15072, Perú</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>15072</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>-12.0779355</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-77.0404273</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>CURRENT_URL_EXACT</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Edgardo Rebagliati Martins National Hospital Lima Peru</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>peru</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Hospital Clínico Universidad de Chile</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Hospital Clínico de la Universidad de Chile</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Chile. | CP - Dr. Carlos Lorca Tobar 999 (ex, Santos Dumont, 8380456 Independencia, Región Metropolitana, Chile</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>8380456</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>-33.420156</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-70.6531104</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>CURRENT_URL_EXACT</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Hospital Clínico Universidad de Chile Santiago Chile</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>chile</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
